--- a/mekko_template.xlsx
+++ b/mekko_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mekko Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Values" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Color" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,34 +30,27 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006b6860"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001a1917"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001a1917"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="002D6A4F"/>
-      <sz val="11"/>
+      <i val="1"/>
+      <color rgb="006B6860"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -64,7 +59,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001a1917"/>
+        <fgColor rgb="001A1917"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F4F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,11 +74,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00f8f7f4"/>
+        <fgColor rgb="00E8F4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBF0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,55 +96,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00dddbd3"/>
-      </left>
-      <right style="thin">
-        <color rgb="00dddbd3"/>
-      </right>
-      <top style="thin">
-        <color rgb="00dddbd3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00dddbd3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,127 +490,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mekko Chart Template — Row 3 onwards is your data. First column = segment names, first data row = column headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Vendor A</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B2" s="4" t="n">
         <v>141658</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>105358</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>177072</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E2" s="4" t="n">
         <v>70829</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Vendor B</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B3" s="6" t="n">
         <v>82634</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C3" s="6" t="n">
         <v>87798</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D3" s="6" t="n">
         <v>47957</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E3" s="6" t="n">
         <v>87798</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Vendor C</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>44268</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>30102</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>41317</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>35414</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B5" s="6" t="n">
         <v>27594</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C5" s="6" t="n">
         <v>27594</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D5" s="6" t="n">
         <v>28774</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E5" s="6" t="n">
         <v>15494</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -632,75 +610,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>How to use this template</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="9" t="inlineStr"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>1. Keep the layout exactly as shown on the 'Mekko Data' sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>2. First column: segment / row names (e.g. Vendor A, Product X)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>3. First data row (row 3): column names (e.g. Q1, Region 1, Year)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>4. Remaining cells: numeric values (no $ signs, no commas needed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>5. Add or remove rows and columns freely — just keep the grid intact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>6. Leave the top-left cell (A3) empty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Drag this file into the Mekko Chart Builder app to load your data.</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Color metric values (e.g. margin %). Same layout as Values sheet. This sheet is optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Vendor A</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Vendor B</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Vendor C</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>